--- a/Financial Analysis/UMAC.xlsx
+++ b/Financial Analysis/UMAC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D3E9CE-8FD2-495F-AAD1-7459105410FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C516DAB0-F8D1-4654-B3B2-6DB4D2B0BA2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{1911E082-F3EB-4149-9E06-B163ACF315BA}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
   <si>
     <t>UMAC</t>
   </si>
@@ -203,16 +203,26 @@
   </si>
   <si>
     <t>Heavily overvalued</t>
+  </si>
+  <si>
+    <t>L+S/E</t>
+  </si>
+  <si>
+    <t>EV/B</t>
+  </si>
+  <si>
+    <t>B/EV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,6 +253,15 @@
     </font>
     <font>
       <i/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -291,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -310,7 +329,9 @@
     <xf numFmtId="2" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -382,14 +403,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -406,7 +427,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7612380" y="7620"/>
+          <a:off x="8229600" y="7620"/>
           <a:ext cx="0" cy="6316980"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -757,14 +778,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>9.0399999999999991</v>
+        <v>14.97</v>
       </c>
       <c r="E3" s="5">
-        <v>45903</v>
+        <v>45933</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45926</v>
+        <v>45933</v>
       </c>
       <c r="G3" s="5">
         <v>45974</v>
@@ -787,7 +808,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>274.81599999999997</v>
+        <v>455.08800000000002</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -828,7 +849,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>269.81599999999997</v>
+        <v>450.08800000000002</v>
       </c>
     </row>
   </sheetData>
@@ -838,7 +859,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B907B56C-692C-4EF6-A389-CF69118537CB}">
-  <dimension ref="B2:EK34"/>
+  <dimension ref="B2:EK36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -3726,24 +3747,49 @@
       </c>
       <c r="AF32" s="4">
         <f>Main!D3</f>
-        <v>9.0399999999999991</v>
-      </c>
-    </row>
-    <row r="33" spans="31:32" x14ac:dyDescent="0.3">
-      <c r="AE33" s="3" t="s">
+        <v>14.97</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="L33" s="12">
+        <f>52.4</f>
+        <v>52.4</v>
+      </c>
+      <c r="AE33" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="AF33" s="12">
+      <c r="AF33" s="13">
         <f>AF31/AF32-1</f>
-        <v>-0.78010157110479306</v>
-      </c>
-    </row>
-    <row r="34" spans="31:32" x14ac:dyDescent="0.3">
+        <v>-0.86720896478205278</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.3">
       <c r="AE34" s="1" t="s">
         <v>56</v>
       </c>
       <c r="AF34" s="7" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L35" s="14">
+        <f>Main!D9/Model!L33</f>
+        <v>8.5894656488549632</v>
+      </c>
+    </row>
+    <row r="36" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L36" s="11">
+        <f>L33/Main!D9-1</f>
+        <v>-0.88357832246138535</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/UMAC.xlsx
+++ b/Financial Analysis/UMAC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C516DAB0-F8D1-4654-B3B2-6DB4D2B0BA2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C6ABCB-B9BE-4A5E-BCF1-550E046D9D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{1911E082-F3EB-4149-9E06-B163ACF315BA}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
   <si>
     <t>UMAC</t>
   </si>
@@ -155,9 +155,6 @@
   </si>
   <si>
     <t>S&amp;M Margin</t>
-  </si>
-  <si>
-    <t>Revenue q/q</t>
   </si>
   <si>
     <t>Q125</t>
@@ -330,8 +327,8 @@
     <xf numFmtId="4" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -361,8 +358,8 @@
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -378,7 +375,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11262360" y="0"/>
-          <a:ext cx="0" cy="6301740"/>
+          <a:ext cx="0" cy="7490460"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -403,16 +400,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -427,8 +424,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8229600" y="7620"/>
-          <a:ext cx="0" cy="6316980"/>
+          <a:off x="8823960" y="7620"/>
+          <a:ext cx="0" cy="7155180"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -778,17 +775,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>14.97</v>
+        <v>7.88</v>
       </c>
       <c r="E3" s="5">
-        <v>45933</v>
+        <v>45983</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45933</v>
+        <v>45983</v>
       </c>
       <c r="G3" s="5">
-        <v>45974</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -796,10 +793,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <v>30.4</v>
+        <f>36.9</f>
+        <v>36.9</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -808,7 +806,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>455.08800000000002</v>
+        <v>290.77199999999999</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -816,11 +814,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <f>5</f>
-        <v>5</v>
+        <f>64.3+16.8</f>
+        <v>81.099999999999994</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -831,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -840,7 +838,7 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>5</v>
+        <v>81.099999999999994</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -849,7 +847,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>450.08800000000002</v>
+        <v>209.672</v>
       </c>
     </row>
   </sheetData>
@@ -859,7 +857,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B907B56C-692C-4EF6-A389-CF69118537CB}">
-  <dimension ref="B2:EK36"/>
+  <dimension ref="B2:EK35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -896,16 +894,16 @@
         <v>37</v>
       </c>
       <c r="K2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="M2" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="N2" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="P2" s="1">
         <v>2023</v>
@@ -980,12 +978,11 @@
         <v>2.1</v>
       </c>
       <c r="M3" s="8">
-        <f>I3*2</f>
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="N3" s="8">
-        <f>J3*2</f>
-        <v>4.1999999999999993</v>
+        <f>J3*1.3</f>
+        <v>2.7299999999999995</v>
       </c>
       <c r="P3" s="8">
         <f>SUM(C3:F3)</f>
@@ -996,47 +993,47 @@
       </c>
       <c r="R3" s="8">
         <f>SUM(K3:N3)</f>
-        <v>11.299999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="S3" s="8">
         <f>R3*2</f>
-        <v>22.599999999999998</v>
+        <v>17.86</v>
       </c>
       <c r="T3" s="8">
         <f>S3*1.9</f>
-        <v>42.939999999999991</v>
+        <v>33.933999999999997</v>
       </c>
       <c r="U3" s="8">
         <f>T3*1.8</f>
-        <v>77.291999999999987</v>
+        <v>61.081199999999995</v>
       </c>
       <c r="V3" s="8">
         <f>U3*1.7</f>
-        <v>131.39639999999997</v>
+        <v>103.83803999999999</v>
       </c>
       <c r="W3" s="8">
         <f>V3*1.6</f>
-        <v>210.23423999999997</v>
+        <v>166.14086399999999</v>
       </c>
       <c r="X3" s="8">
         <f>W3*1.5</f>
-        <v>315.35135999999994</v>
+        <v>249.211296</v>
       </c>
       <c r="Y3" s="8">
         <f>X3*1.4</f>
-        <v>441.49190399999992</v>
+        <v>348.89581440000001</v>
       </c>
       <c r="Z3" s="8">
         <f>Y3*1.3</f>
-        <v>573.93947519999995</v>
+        <v>453.56455872000004</v>
       </c>
       <c r="AA3" s="8">
         <f>Z3*1.2</f>
-        <v>688.72737023999991</v>
+        <v>544.27747046399998</v>
       </c>
       <c r="AB3" s="8">
-        <f t="shared" ref="AB3" si="0">AA3*1.2</f>
-        <v>826.47284428799992</v>
+        <f>AA3*1.15</f>
+        <v>625.9190910335999</v>
       </c>
     </row>
     <row r="4" spans="2:28" x14ac:dyDescent="0.3">
@@ -1072,12 +1069,11 @@
         <v>1.3</v>
       </c>
       <c r="M4" s="6">
-        <f t="shared" ref="M4:N4" si="1">M3-M5</f>
-        <v>2.16</v>
+        <v>1.3</v>
       </c>
       <c r="N4" s="6">
-        <f t="shared" si="1"/>
-        <v>3.1079999999999997</v>
+        <f t="shared" ref="N4" si="0">N3-N5</f>
+        <v>1.9109999999999996</v>
       </c>
       <c r="P4" s="6">
         <f>SUM(C4:F4)</f>
@@ -1088,47 +1084,47 @@
       </c>
       <c r="R4" s="6">
         <f>SUM(K4:N4)</f>
-        <v>8.0679999999999996</v>
+        <v>6.0109999999999992</v>
       </c>
       <c r="S4" s="6">
         <f>S3-S5</f>
-        <v>15.819999999999999</v>
+        <v>12.501999999999999</v>
       </c>
       <c r="T4" s="6">
-        <f t="shared" ref="T4:AB4" si="2">T3-T5</f>
-        <v>30.057999999999993</v>
+        <f t="shared" ref="T4:AB4" si="1">T3-T5</f>
+        <v>23.753799999999998</v>
       </c>
       <c r="U4" s="6">
-        <f t="shared" si="2"/>
-        <v>54.104399999999991</v>
+        <f t="shared" si="1"/>
+        <v>42.756839999999997</v>
       </c>
       <c r="V4" s="6">
-        <f t="shared" si="2"/>
-        <v>91.977479999999986</v>
+        <f t="shared" si="1"/>
+        <v>72.686627999999999</v>
       </c>
       <c r="W4" s="6">
-        <f t="shared" si="2"/>
-        <v>147.16396799999998</v>
+        <f t="shared" si="1"/>
+        <v>116.29860479999999</v>
       </c>
       <c r="X4" s="6">
-        <f t="shared" si="2"/>
-        <v>220.74595199999996</v>
+        <f t="shared" si="1"/>
+        <v>174.4479072</v>
       </c>
       <c r="Y4" s="6">
-        <f t="shared" si="2"/>
-        <v>309.04433279999995</v>
+        <f t="shared" si="1"/>
+        <v>244.22707008</v>
       </c>
       <c r="Z4" s="6">
-        <f t="shared" si="2"/>
-        <v>401.75763264</v>
+        <f t="shared" si="1"/>
+        <v>317.49519110400001</v>
       </c>
       <c r="AA4" s="6">
-        <f t="shared" si="2"/>
-        <v>482.10915916799991</v>
+        <f t="shared" si="1"/>
+        <v>380.99422932480002</v>
       </c>
       <c r="AB4" s="6">
-        <f t="shared" si="2"/>
-        <v>578.53099100159989</v>
+        <f t="shared" si="1"/>
+        <v>438.14336372351994</v>
       </c>
     </row>
     <row r="5" spans="2:28" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1172,12 +1168,12 @@
         <v>0.8</v>
       </c>
       <c r="M5" s="8">
-        <f>M3*0.28</f>
-        <v>0.84000000000000008</v>
+        <f>M3-M4</f>
+        <v>0.8</v>
       </c>
       <c r="N5" s="8">
-        <f>N3*0.26</f>
-        <v>1.0919999999999999</v>
+        <f>N3*0.3</f>
+        <v>0.81899999999999984</v>
       </c>
       <c r="P5" s="8">
         <f>P3-P4</f>
@@ -1189,47 +1185,47 @@
       </c>
       <c r="R5" s="8">
         <f>R3-R4</f>
-        <v>3.2319999999999993</v>
+        <v>2.9190000000000005</v>
       </c>
       <c r="S5" s="8">
         <f>S3*0.3</f>
-        <v>6.7799999999999994</v>
+        <v>5.3579999999999997</v>
       </c>
       <c r="T5" s="8">
-        <f t="shared" ref="T5:AB5" si="3">T3*0.3</f>
-        <v>12.881999999999996</v>
+        <f t="shared" ref="T5:AB5" si="2">T3*0.3</f>
+        <v>10.180199999999999</v>
       </c>
       <c r="U5" s="8">
-        <f t="shared" si="3"/>
-        <v>23.187599999999996</v>
+        <f t="shared" si="2"/>
+        <v>18.324359999999999</v>
       </c>
       <c r="V5" s="8">
-        <f t="shared" si="3"/>
-        <v>39.418919999999993</v>
+        <f t="shared" si="2"/>
+        <v>31.151411999999997</v>
       </c>
       <c r="W5" s="8">
-        <f t="shared" si="3"/>
-        <v>63.070271999999989</v>
+        <f t="shared" si="2"/>
+        <v>49.842259199999994</v>
       </c>
       <c r="X5" s="8">
-        <f t="shared" si="3"/>
-        <v>94.605407999999983</v>
+        <f t="shared" si="2"/>
+        <v>74.763388800000001</v>
       </c>
       <c r="Y5" s="8">
-        <f t="shared" si="3"/>
-        <v>132.44757119999997</v>
+        <f t="shared" si="2"/>
+        <v>104.66874432</v>
       </c>
       <c r="Z5" s="8">
-        <f t="shared" si="3"/>
-        <v>172.18184255999998</v>
+        <f t="shared" si="2"/>
+        <v>136.06936761599999</v>
       </c>
       <c r="AA5" s="8">
-        <f t="shared" si="3"/>
-        <v>206.61821107199998</v>
+        <f t="shared" si="2"/>
+        <v>163.28324113919999</v>
       </c>
       <c r="AB5" s="8">
-        <f t="shared" si="3"/>
-        <v>247.94185328639998</v>
+        <f t="shared" si="2"/>
+        <v>187.77572731007996</v>
       </c>
     </row>
     <row r="6" spans="2:28" x14ac:dyDescent="0.3">
@@ -1255,7 +1251,7 @@
         <v>0.2</v>
       </c>
       <c r="J6" s="6">
-        <f t="shared" ref="J6:J10" si="4">Q6-I6-H6-G6</f>
+        <f t="shared" ref="J6:J10" si="3">Q6-I6-H6-G6</f>
         <v>0.50000000000000011</v>
       </c>
       <c r="K6" s="6">
@@ -1265,7 +1261,7 @@
         <v>0.4</v>
       </c>
       <c r="M6" s="6">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="N6" s="6">
         <v>0</v>
@@ -1279,7 +1275,7 @@
       </c>
       <c r="R6" s="6">
         <f>SUM(K6:N6)</f>
-        <v>0.7</v>
+        <v>1.2999999999999998</v>
       </c>
       <c r="S6" s="6">
         <v>0</v>
@@ -1335,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
       <c r="K7" s="6">
@@ -1415,7 +1411,7 @@
         <v>0.3</v>
       </c>
       <c r="J8" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
       <c r="K8" s="6">
@@ -1425,12 +1421,11 @@
         <v>0.3</v>
       </c>
       <c r="M8" s="6">
-        <f t="shared" ref="M8:N8" si="5">M3*0.3</f>
-        <v>0.89999999999999991</v>
+        <v>0.4</v>
       </c>
       <c r="N8" s="6">
-        <f t="shared" si="5"/>
-        <v>1.2599999999999998</v>
+        <f t="shared" ref="N8" si="4">N3*0.3</f>
+        <v>0.81899999999999984</v>
       </c>
       <c r="P8" s="6">
         <f>SUM(C8:F8)</f>
@@ -1441,47 +1436,47 @@
       </c>
       <c r="R8" s="6">
         <f>SUM(K8:N8)</f>
-        <v>2.6599999999999997</v>
+        <v>1.7189999999999999</v>
       </c>
       <c r="S8" s="6">
         <f>S3*0.25</f>
-        <v>5.6499999999999995</v>
+        <v>4.4649999999999999</v>
       </c>
       <c r="T8" s="6">
         <f>T3*0.23</f>
-        <v>9.876199999999999</v>
+        <v>7.8048199999999994</v>
       </c>
       <c r="U8" s="6">
         <f>U3*0.21</f>
-        <v>16.231319999999997</v>
+        <v>12.827051999999998</v>
       </c>
       <c r="V8" s="6">
         <f>V3*0.19</f>
-        <v>24.965315999999994</v>
+        <v>19.729227599999998</v>
       </c>
       <c r="W8" s="6">
         <f>W3*0.18</f>
-        <v>37.842163199999995</v>
+        <v>29.905355519999997</v>
       </c>
       <c r="X8" s="6">
         <f>X3*0.17</f>
-        <v>53.609731199999992</v>
+        <v>42.365920320000001</v>
       </c>
       <c r="Y8" s="6">
         <f>Y3*0.16</f>
-        <v>70.638704639999986</v>
+        <v>55.823330304000002</v>
       </c>
       <c r="Z8" s="6">
         <f>Z3*0.16</f>
-        <v>91.830316031999999</v>
+        <v>72.570329395200005</v>
       </c>
       <c r="AA8" s="6">
         <f>AA3*0.15</f>
-        <v>103.30910553599999</v>
+        <v>81.641620569599993</v>
       </c>
       <c r="AB8" s="6">
         <f>AB3*0.14</f>
-        <v>115.70619820032</v>
+        <v>87.628672744703991</v>
       </c>
     </row>
     <row r="9" spans="2:28" x14ac:dyDescent="0.3">
@@ -1507,7 +1502,7 @@
         <v>1.4</v>
       </c>
       <c r="J9" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.6000000000000005</v>
       </c>
       <c r="K9" s="6">
@@ -1517,10 +1512,10 @@
         <v>7.2</v>
       </c>
       <c r="M9" s="6">
-        <v>8</v>
+        <v>4.7</v>
       </c>
       <c r="N9" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P9" s="6">
         <f>SUM(C9:F9)</f>
@@ -1531,47 +1526,47 @@
       </c>
       <c r="R9" s="6">
         <f>SUM(K9:N9)</f>
-        <v>27.4</v>
+        <v>22.1</v>
       </c>
       <c r="S9" s="6">
-        <f>R9*1.3</f>
-        <v>35.619999999999997</v>
+        <f>R9*1.05</f>
+        <v>23.205000000000002</v>
       </c>
       <c r="T9" s="6">
         <f>S9*1.2</f>
-        <v>42.743999999999993</v>
+        <v>27.846</v>
       </c>
       <c r="U9" s="6">
         <f>T9*0.8</f>
-        <v>34.195199999999993</v>
+        <v>22.276800000000001</v>
       </c>
       <c r="V9" s="6">
         <f>U9*0.8</f>
-        <v>27.356159999999996</v>
+        <v>17.821440000000003</v>
       </c>
       <c r="W9" s="6">
         <f>V9*1.1</f>
-        <v>30.091775999999996</v>
+        <v>19.603584000000005</v>
       </c>
       <c r="X9" s="6">
-        <f t="shared" ref="X9:Y9" si="6">W9*1.1</f>
-        <v>33.100953599999997</v>
+        <f t="shared" ref="X9:Y9" si="5">W9*1.1</f>
+        <v>21.563942400000006</v>
       </c>
       <c r="Y9" s="6">
-        <f t="shared" si="6"/>
-        <v>36.411048960000002</v>
+        <f t="shared" si="5"/>
+        <v>23.720336640000006</v>
       </c>
       <c r="Z9" s="6">
         <f>Y9*1.05</f>
-        <v>38.231601408000003</v>
+        <v>24.906353472000006</v>
       </c>
       <c r="AA9" s="6">
-        <f t="shared" ref="AA9:AB9" si="7">Z9*1.05</f>
-        <v>40.143181478400003</v>
+        <f t="shared" ref="AA9:AB9" si="6">Z9*1.05</f>
+        <v>26.151671145600009</v>
       </c>
       <c r="AB9" s="6">
-        <f t="shared" si="7"/>
-        <v>42.150340552320003</v>
+        <f t="shared" si="6"/>
+        <v>27.45925470288001</v>
       </c>
     </row>
     <row r="10" spans="2:28" x14ac:dyDescent="0.3">
@@ -1597,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>10.199999999999999</v>
       </c>
       <c r="K10" s="6">
@@ -1688,20 +1683,20 @@
         <v>13.6</v>
       </c>
       <c r="K11" s="6">
-        <f t="shared" ref="K11:N11" si="8">SUM(K6:K10)</f>
+        <f t="shared" ref="K11:N11" si="7">SUM(K6:K10)</f>
         <v>3.7</v>
       </c>
       <c r="L11" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="M11" s="6">
-        <f t="shared" si="8"/>
-        <v>8.9</v>
+        <f t="shared" si="7"/>
+        <v>5.7</v>
       </c>
       <c r="N11" s="6">
-        <f t="shared" si="8"/>
-        <v>10.26</v>
+        <f t="shared" si="7"/>
+        <v>7.819</v>
       </c>
       <c r="P11" s="6">
         <f>SUM(P6:P10)</f>
@@ -1713,47 +1708,47 @@
       </c>
       <c r="R11" s="6">
         <f>SUM(R6:R10)</f>
-        <v>30.86</v>
+        <v>25.219000000000001</v>
       </c>
       <c r="S11" s="6">
         <f>SUM(S6:S10)</f>
-        <v>43.269999999999996</v>
+        <v>29.67</v>
       </c>
       <c r="T11" s="6">
-        <f t="shared" ref="T11:AB11" si="9">SUM(T6:T10)</f>
-        <v>57.62019999999999</v>
+        <f t="shared" ref="T11:AB11" si="8">SUM(T6:T10)</f>
+        <v>40.650819999999996</v>
       </c>
       <c r="U11" s="6">
-        <f t="shared" si="9"/>
-        <v>59.426519999999989</v>
+        <f t="shared" si="8"/>
+        <v>44.103852000000003</v>
       </c>
       <c r="V11" s="6">
-        <f t="shared" si="9"/>
-        <v>65.32147599999999</v>
+        <f t="shared" si="8"/>
+        <v>50.550667600000004</v>
       </c>
       <c r="W11" s="6">
-        <f t="shared" si="9"/>
-        <v>82.933939199999998</v>
+        <f t="shared" si="8"/>
+        <v>64.508939520000013</v>
       </c>
       <c r="X11" s="6">
-        <f t="shared" si="9"/>
-        <v>103.7106848</v>
+        <f t="shared" si="8"/>
+        <v>80.929862720000003</v>
       </c>
       <c r="Y11" s="6">
-        <f t="shared" si="9"/>
-        <v>126.04975359999999</v>
+        <f t="shared" si="8"/>
+        <v>98.543666943999995</v>
       </c>
       <c r="Z11" s="6">
-        <f t="shared" si="9"/>
-        <v>150.06191744</v>
+        <f t="shared" si="8"/>
+        <v>117.47668286720001</v>
       </c>
       <c r="AA11" s="6">
-        <f t="shared" si="9"/>
-        <v>164.45228701439999</v>
+        <f t="shared" si="8"/>
+        <v>128.79329171520001</v>
       </c>
       <c r="AB11" s="6">
-        <f t="shared" si="9"/>
-        <v>179.85653875264001</v>
+        <f t="shared" si="8"/>
+        <v>137.08792744758401</v>
       </c>
     </row>
     <row r="12" spans="2:28" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1789,20 +1784,20 @@
         <v>-13.074999999999999</v>
       </c>
       <c r="K12" s="8">
-        <f t="shared" ref="K12:N12" si="10">K5-K11</f>
+        <f t="shared" ref="K12:N12" si="9">K5-K11</f>
         <v>-3.2</v>
       </c>
       <c r="L12" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>-7.2</v>
       </c>
       <c r="M12" s="8">
-        <f t="shared" si="10"/>
-        <v>-8.06</v>
+        <f t="shared" si="9"/>
+        <v>-4.9000000000000004</v>
       </c>
       <c r="N12" s="8">
-        <f t="shared" si="10"/>
-        <v>-9.1679999999999993</v>
+        <f t="shared" si="9"/>
+        <v>-7</v>
       </c>
       <c r="P12" s="8">
         <f>P5-P11</f>
@@ -1814,47 +1809,47 @@
       </c>
       <c r="R12" s="8">
         <f>R5-R11</f>
-        <v>-27.628</v>
+        <v>-22.3</v>
       </c>
       <c r="S12" s="8">
         <f>S5-S11</f>
-        <v>-36.489999999999995</v>
+        <v>-24.312000000000001</v>
       </c>
       <c r="T12" s="8">
-        <f t="shared" ref="T12:AB12" si="11">T5-T11</f>
-        <v>-44.738199999999992</v>
+        <f t="shared" ref="T12:AB12" si="10">T5-T11</f>
+        <v>-30.470619999999997</v>
       </c>
       <c r="U12" s="8">
-        <f t="shared" si="11"/>
-        <v>-36.238919999999993</v>
+        <f t="shared" si="10"/>
+        <v>-25.779492000000005</v>
       </c>
       <c r="V12" s="8">
-        <f t="shared" si="11"/>
-        <v>-25.902555999999997</v>
+        <f t="shared" si="10"/>
+        <v>-19.399255600000007</v>
       </c>
       <c r="W12" s="8">
-        <f t="shared" si="11"/>
-        <v>-19.863667200000009</v>
+        <f t="shared" si="10"/>
+        <v>-14.666680320000019</v>
       </c>
       <c r="X12" s="8">
-        <f t="shared" si="11"/>
-        <v>-9.1052768000000128</v>
+        <f t="shared" si="10"/>
+        <v>-6.1664739200000014</v>
       </c>
       <c r="Y12" s="8">
-        <f t="shared" si="11"/>
-        <v>6.397817599999982</v>
+        <f t="shared" si="10"/>
+        <v>6.1250773760000072</v>
       </c>
       <c r="Z12" s="8">
-        <f t="shared" si="11"/>
-        <v>22.119925119999976</v>
+        <f t="shared" si="10"/>
+        <v>18.592684748799982</v>
       </c>
       <c r="AA12" s="8">
-        <f t="shared" si="11"/>
-        <v>42.165924057599995</v>
+        <f t="shared" si="10"/>
+        <v>34.489949423999974</v>
       </c>
       <c r="AB12" s="8">
-        <f t="shared" si="11"/>
-        <v>68.08531453375997</v>
+        <f t="shared" si="10"/>
+        <v>50.68779986249595</v>
       </c>
     </row>
     <row r="13" spans="2:28" x14ac:dyDescent="0.3">
@@ -1880,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="6">
-        <f t="shared" ref="J13:J16" si="12">Q13-I13-H13-G13</f>
+        <f t="shared" ref="J13:J16" si="11">Q13-I13-H13-G13</f>
         <v>0</v>
       </c>
       <c r="K13" s="6">
@@ -1890,7 +1885,7 @@
         <v>-0.2</v>
       </c>
       <c r="M13" s="6">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="N13" s="6">
         <v>0</v>
@@ -1904,7 +1899,7 @@
       </c>
       <c r="R13" s="6">
         <f>SUM(K13:N13)</f>
-        <v>-0.2</v>
+        <v>-0.89999999999999991</v>
       </c>
       <c r="S13" s="6">
         <v>0</v>
@@ -1960,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0.1</v>
       </c>
       <c r="K14" s="6">
@@ -1970,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="6">
-        <v>0</v>
+        <v>-5.8</v>
       </c>
       <c r="N14" s="6">
         <v>0</v>
@@ -1984,7 +1979,7 @@
       </c>
       <c r="R14" s="6">
         <f>SUM(K14:N14)</f>
-        <v>0</v>
+        <v>-5.8</v>
       </c>
       <c r="S14" s="6">
         <v>0</v>
@@ -2040,7 +2035,7 @@
         <v>0.7</v>
       </c>
       <c r="J15" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>15.400000000000002</v>
       </c>
       <c r="K15" s="6">
@@ -2120,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>-1.3</v>
       </c>
       <c r="K16" s="6">
@@ -2210,19 +2205,19 @@
         <v>14.200000000000001</v>
       </c>
       <c r="K17" s="6">
-        <f t="shared" ref="K17:N17" si="13">SUM(K13:K16)</f>
+        <f t="shared" ref="K17:N17" si="12">SUM(K13:K16)</f>
         <v>0</v>
       </c>
       <c r="L17" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-0.2</v>
       </c>
       <c r="M17" s="6">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>-6.5</v>
       </c>
       <c r="N17" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="P17" s="6">
@@ -2235,46 +2230,46 @@
       </c>
       <c r="R17" s="6">
         <f>SUM(R13:R16)</f>
-        <v>-0.2</v>
+        <v>-6.6999999999999993</v>
       </c>
       <c r="S17" s="6">
         <f>SUM(S13:S16)</f>
         <v>0</v>
       </c>
       <c r="T17" s="6">
-        <f t="shared" ref="T17:AB17" si="14">SUM(T13:T16)</f>
+        <f t="shared" ref="T17:AB17" si="13">SUM(T13:T16)</f>
         <v>0</v>
       </c>
       <c r="U17" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="V17" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="W17" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="X17" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="Y17" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="Z17" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AA17" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AB17" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -2311,20 +2306,20 @@
         <v>-27.274999999999999</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" ref="K18:N18" si="15">K12-K17</f>
+        <f t="shared" ref="K18:N18" si="14">K12-K17</f>
         <v>-3.2</v>
       </c>
       <c r="L18" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>-7</v>
       </c>
       <c r="M18" s="8">
-        <f t="shared" si="15"/>
-        <v>-8.06</v>
+        <f t="shared" si="14"/>
+        <v>1.5999999999999996</v>
       </c>
       <c r="N18" s="8">
-        <f t="shared" si="15"/>
-        <v>-9.1679999999999993</v>
+        <f t="shared" si="14"/>
+        <v>-7</v>
       </c>
       <c r="P18" s="8">
         <f>P12-P17</f>
@@ -2336,47 +2331,47 @@
       </c>
       <c r="R18" s="8">
         <f>R12-R17</f>
-        <v>-27.428000000000001</v>
+        <v>-15.600000000000001</v>
       </c>
       <c r="S18" s="8">
         <f>S12-S17</f>
-        <v>-36.489999999999995</v>
+        <v>-24.312000000000001</v>
       </c>
       <c r="T18" s="8">
-        <f t="shared" ref="T18:AB18" si="16">T12-T17</f>
-        <v>-44.738199999999992</v>
+        <f t="shared" ref="T18:AB18" si="15">T12-T17</f>
+        <v>-30.470619999999997</v>
       </c>
       <c r="U18" s="8">
-        <f t="shared" si="16"/>
-        <v>-36.238919999999993</v>
+        <f t="shared" si="15"/>
+        <v>-25.779492000000005</v>
       </c>
       <c r="V18" s="8">
-        <f t="shared" si="16"/>
-        <v>-25.902555999999997</v>
+        <f t="shared" si="15"/>
+        <v>-19.399255600000007</v>
       </c>
       <c r="W18" s="8">
-        <f t="shared" si="16"/>
-        <v>-19.863667200000009</v>
+        <f t="shared" si="15"/>
+        <v>-14.666680320000019</v>
       </c>
       <c r="X18" s="8">
-        <f t="shared" si="16"/>
-        <v>-9.1052768000000128</v>
+        <f t="shared" si="15"/>
+        <v>-6.1664739200000014</v>
       </c>
       <c r="Y18" s="8">
-        <f t="shared" si="16"/>
-        <v>6.397817599999982</v>
+        <f t="shared" si="15"/>
+        <v>6.1250773760000072</v>
       </c>
       <c r="Z18" s="8">
-        <f t="shared" si="16"/>
-        <v>22.119925119999976</v>
+        <f t="shared" si="15"/>
+        <v>18.592684748799982</v>
       </c>
       <c r="AA18" s="8">
-        <f t="shared" si="16"/>
-        <v>42.165924057599995</v>
+        <f t="shared" si="15"/>
+        <v>34.489949423999974</v>
       </c>
       <c r="AB18" s="8">
-        <f t="shared" si="16"/>
-        <v>68.08531453375997</v>
+        <f t="shared" si="15"/>
+        <v>50.68779986249595</v>
       </c>
     </row>
     <row r="19" spans="2:141" x14ac:dyDescent="0.3">
@@ -2492,20 +2487,20 @@
         <v>-27.274999999999999</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" ref="K20:N20" si="17">K18-K19</f>
+        <f t="shared" ref="K20:N20" si="16">K18-K19</f>
         <v>-3.2</v>
       </c>
       <c r="L20" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-7</v>
       </c>
       <c r="M20" s="8">
-        <f t="shared" si="17"/>
-        <v>-8.06</v>
+        <f t="shared" si="16"/>
+        <v>1.5999999999999996</v>
       </c>
       <c r="N20" s="8">
-        <f t="shared" si="17"/>
-        <v>-9.1679999999999993</v>
+        <f t="shared" si="16"/>
+        <v>-7</v>
       </c>
       <c r="P20" s="8">
         <f>P18-P19</f>
@@ -2517,499 +2512,499 @@
       </c>
       <c r="R20" s="8">
         <f>R18-R19</f>
-        <v>-27.428000000000001</v>
+        <v>-15.600000000000001</v>
       </c>
       <c r="S20" s="8">
         <f>S18-S19</f>
-        <v>-36.489999999999995</v>
+        <v>-24.312000000000001</v>
       </c>
       <c r="T20" s="8">
-        <f t="shared" ref="T20:AB20" si="18">T18-T19</f>
-        <v>-44.738199999999992</v>
+        <f t="shared" ref="T20:AB20" si="17">T18-T19</f>
+        <v>-30.470619999999997</v>
       </c>
       <c r="U20" s="8">
-        <f t="shared" si="18"/>
-        <v>-36.238919999999993</v>
+        <f t="shared" si="17"/>
+        <v>-25.779492000000005</v>
       </c>
       <c r="V20" s="8">
-        <f t="shared" si="18"/>
-        <v>-25.902555999999997</v>
+        <f t="shared" si="17"/>
+        <v>-19.399255600000007</v>
       </c>
       <c r="W20" s="8">
-        <f t="shared" si="18"/>
-        <v>-19.863667200000009</v>
+        <f t="shared" si="17"/>
+        <v>-14.666680320000019</v>
       </c>
       <c r="X20" s="8">
-        <f t="shared" si="18"/>
-        <v>-9.1052768000000128</v>
+        <f t="shared" si="17"/>
+        <v>-6.1664739200000014</v>
       </c>
       <c r="Y20" s="8">
-        <f t="shared" si="18"/>
-        <v>6.397817599999982</v>
+        <f t="shared" si="17"/>
+        <v>6.1250773760000072</v>
       </c>
       <c r="Z20" s="8">
-        <f t="shared" si="18"/>
-        <v>22.119925119999976</v>
+        <f t="shared" si="17"/>
+        <v>18.592684748799982</v>
       </c>
       <c r="AA20" s="8">
-        <f t="shared" si="18"/>
-        <v>42.165924057599995</v>
+        <f t="shared" si="17"/>
+        <v>34.489949423999974</v>
       </c>
       <c r="AB20" s="8">
-        <f t="shared" si="18"/>
-        <v>68.08531453375997</v>
+        <f t="shared" si="17"/>
+        <v>50.68779986249595</v>
       </c>
       <c r="AC20" s="3">
-        <f>AB20*(1+$AF$26)</f>
-        <v>67.404461388422376</v>
+        <f>AB20*(1+$AF$25)</f>
+        <v>50.180921863870992</v>
       </c>
       <c r="AD20" s="3">
-        <f t="shared" ref="AD20:CO20" si="19">AC20*(1+$AF$26)</f>
-        <v>66.730416774538156</v>
+        <f t="shared" ref="AD20:CO20" si="18">AC20*(1+$AF$25)</f>
+        <v>49.67911264523228</v>
       </c>
       <c r="AE20" s="3">
-        <f t="shared" si="19"/>
-        <v>66.063112606792771</v>
+        <f t="shared" si="18"/>
+        <v>49.182321518779958</v>
       </c>
       <c r="AF20" s="3">
-        <f t="shared" si="19"/>
-        <v>65.402481480724845</v>
+        <f t="shared" si="18"/>
+        <v>48.690498303592157</v>
       </c>
       <c r="AG20" s="3">
-        <f t="shared" si="19"/>
-        <v>64.748456665917601</v>
+        <f t="shared" si="18"/>
+        <v>48.203593320556237</v>
       </c>
       <c r="AH20" s="3">
-        <f t="shared" si="19"/>
-        <v>64.100972099258428</v>
+        <f t="shared" si="18"/>
+        <v>47.721557387350671</v>
       </c>
       <c r="AI20" s="3">
-        <f t="shared" si="19"/>
-        <v>63.459962378265843</v>
+        <f t="shared" si="18"/>
+        <v>47.244341813477163</v>
       </c>
       <c r="AJ20" s="3">
-        <f t="shared" si="19"/>
-        <v>62.825362754483187</v>
+        <f t="shared" si="18"/>
+        <v>46.77189839534239</v>
       </c>
       <c r="AK20" s="3">
-        <f t="shared" si="19"/>
-        <v>62.197109126938358</v>
+        <f t="shared" si="18"/>
+        <v>46.304179411388965</v>
       </c>
       <c r="AL20" s="3">
-        <f t="shared" si="19"/>
-        <v>61.575138035668971</v>
+        <f t="shared" si="18"/>
+        <v>45.841137617275074</v>
       </c>
       <c r="AM20" s="3">
-        <f t="shared" si="19"/>
-        <v>60.959386655312279</v>
+        <f t="shared" si="18"/>
+        <v>45.382726241102326</v>
       </c>
       <c r="AN20" s="3">
-        <f t="shared" si="19"/>
-        <v>60.349792788759153</v>
+        <f t="shared" si="18"/>
+        <v>44.928898978691301</v>
       </c>
       <c r="AO20" s="3">
-        <f t="shared" si="19"/>
-        <v>59.746294860871558</v>
+        <f t="shared" si="18"/>
+        <v>44.479609988904386</v>
       </c>
       <c r="AP20" s="3">
-        <f t="shared" si="19"/>
-        <v>59.148831912262843</v>
+        <f t="shared" si="18"/>
+        <v>44.034813889015339</v>
       </c>
       <c r="AQ20" s="3">
-        <f t="shared" si="19"/>
-        <v>58.55734359314021</v>
+        <f t="shared" si="18"/>
+        <v>43.594465750125188</v>
       </c>
       <c r="AR20" s="3">
-        <f t="shared" si="19"/>
-        <v>57.971770157208809</v>
+        <f t="shared" si="18"/>
+        <v>43.158521092623936</v>
       </c>
       <c r="AS20" s="3">
-        <f t="shared" si="19"/>
-        <v>57.392052455636723</v>
+        <f t="shared" si="18"/>
+        <v>42.726935881697699</v>
       </c>
       <c r="AT20" s="3">
-        <f t="shared" si="19"/>
-        <v>56.818131931080352</v>
+        <f t="shared" si="18"/>
+        <v>42.29966652288072</v>
       </c>
       <c r="AU20" s="3">
-        <f t="shared" si="19"/>
-        <v>56.249950611769549</v>
+        <f t="shared" si="18"/>
+        <v>41.876669857651912</v>
       </c>
       <c r="AV20" s="3">
-        <f t="shared" si="19"/>
-        <v>55.687451105651853</v>
+        <f t="shared" si="18"/>
+        <v>41.457903159075393</v>
       </c>
       <c r="AW20" s="3">
-        <f t="shared" si="19"/>
-        <v>55.130576594595333</v>
+        <f t="shared" si="18"/>
+        <v>41.043324127484638</v>
       </c>
       <c r="AX20" s="3">
-        <f t="shared" si="19"/>
-        <v>54.579270828649378</v>
+        <f t="shared" si="18"/>
+        <v>40.632890886209793</v>
       </c>
       <c r="AY20" s="3">
-        <f t="shared" si="19"/>
-        <v>54.033478120362886</v>
+        <f t="shared" si="18"/>
+        <v>40.226561977347693</v>
       </c>
       <c r="AZ20" s="3">
-        <f t="shared" si="19"/>
-        <v>53.493143339159261</v>
+        <f t="shared" si="18"/>
+        <v>39.824296357574212</v>
       </c>
       <c r="BA20" s="3">
-        <f t="shared" si="19"/>
-        <v>52.958211905767669</v>
+        <f t="shared" si="18"/>
+        <v>39.426053393998473</v>
       </c>
       <c r="BB20" s="3">
-        <f t="shared" si="19"/>
-        <v>52.42862978670999</v>
+        <f t="shared" si="18"/>
+        <v>39.031792860058488</v>
       </c>
       <c r="BC20" s="3">
-        <f t="shared" si="19"/>
-        <v>51.904343488842891</v>
+        <f t="shared" si="18"/>
+        <v>38.6414749314579</v>
       </c>
       <c r="BD20" s="3">
-        <f t="shared" si="19"/>
-        <v>51.38530005395446</v>
+        <f t="shared" si="18"/>
+        <v>38.255060182143318</v>
       </c>
       <c r="BE20" s="3">
-        <f t="shared" si="19"/>
-        <v>50.871447053414911</v>
+        <f t="shared" si="18"/>
+        <v>37.872509580321882</v>
       </c>
       <c r="BF20" s="3">
-        <f t="shared" si="19"/>
-        <v>50.36273258288076</v>
+        <f t="shared" si="18"/>
+        <v>37.493784484518663</v>
       </c>
       <c r="BG20" s="3">
-        <f t="shared" si="19"/>
-        <v>49.859105257051951</v>
+        <f t="shared" si="18"/>
+        <v>37.118846639673478</v>
       </c>
       <c r="BH20" s="3">
-        <f t="shared" si="19"/>
-        <v>49.360514204481433</v>
+        <f t="shared" si="18"/>
+        <v>36.74765817327674</v>
       </c>
       <c r="BI20" s="3">
-        <f t="shared" si="19"/>
-        <v>48.866909062436619</v>
+        <f t="shared" si="18"/>
+        <v>36.380181591543973</v>
       </c>
       <c r="BJ20" s="3">
-        <f t="shared" si="19"/>
-        <v>48.378239971812249</v>
+        <f t="shared" si="18"/>
+        <v>36.016379775628536</v>
       </c>
       <c r="BK20" s="3">
-        <f t="shared" si="19"/>
-        <v>47.894457572094126</v>
+        <f t="shared" si="18"/>
+        <v>35.65621597787225</v>
       </c>
       <c r="BL20" s="3">
-        <f t="shared" si="19"/>
-        <v>47.415512996373181</v>
+        <f t="shared" si="18"/>
+        <v>35.299653818093525</v>
       </c>
       <c r="BM20" s="3">
-        <f t="shared" si="19"/>
-        <v>46.941357866409447</v>
+        <f t="shared" si="18"/>
+        <v>34.946657279912586</v>
       </c>
       <c r="BN20" s="3">
-        <f t="shared" si="19"/>
-        <v>46.471944287745352</v>
+        <f t="shared" si="18"/>
+        <v>34.597190707113462</v>
       </c>
       <c r="BO20" s="3">
-        <f t="shared" si="19"/>
-        <v>46.007224844867899</v>
+        <f t="shared" si="18"/>
+        <v>34.251218800042331</v>
       </c>
       <c r="BP20" s="3">
-        <f t="shared" si="19"/>
-        <v>45.547152596419217</v>
+        <f t="shared" si="18"/>
+        <v>33.908706612041904</v>
       </c>
       <c r="BQ20" s="3">
-        <f t="shared" si="19"/>
-        <v>45.091681070455024</v>
+        <f t="shared" si="18"/>
+        <v>33.569619545921483</v>
       </c>
       <c r="BR20" s="3">
-        <f t="shared" si="19"/>
-        <v>44.640764259750476</v>
+        <f t="shared" si="18"/>
+        <v>33.23392335046227</v>
       </c>
       <c r="BS20" s="3">
-        <f t="shared" si="19"/>
-        <v>44.19435661715297</v>
+        <f t="shared" si="18"/>
+        <v>32.901584116957643</v>
       </c>
       <c r="BT20" s="3">
-        <f t="shared" si="19"/>
-        <v>43.752413050981438</v>
+        <f t="shared" si="18"/>
+        <v>32.572568275788065</v>
       </c>
       <c r="BU20" s="3">
-        <f t="shared" si="19"/>
-        <v>43.314888920471624</v>
+        <f t="shared" si="18"/>
+        <v>32.246842593030181</v>
       </c>
       <c r="BV20" s="3">
-        <f t="shared" si="19"/>
-        <v>42.881740031266908</v>
+        <f t="shared" si="18"/>
+        <v>31.924374167099877</v>
       </c>
       <c r="BW20" s="3">
-        <f t="shared" si="19"/>
-        <v>42.452922630954241</v>
+        <f t="shared" si="18"/>
+        <v>31.605130425428879</v>
       </c>
       <c r="BX20" s="3">
-        <f t="shared" si="19"/>
-        <v>42.028393404644696</v>
+        <f t="shared" si="18"/>
+        <v>31.289079121174591</v>
       </c>
       <c r="BY20" s="3">
-        <f t="shared" si="19"/>
-        <v>41.608109470598251</v>
+        <f t="shared" si="18"/>
+        <v>30.976188329962845</v>
       </c>
       <c r="BZ20" s="3">
-        <f t="shared" si="19"/>
-        <v>41.192028375892271</v>
+        <f t="shared" si="18"/>
+        <v>30.666426446663216</v>
       </c>
       <c r="CA20" s="3">
-        <f t="shared" si="19"/>
-        <v>40.780108092133347</v>
+        <f t="shared" si="18"/>
+        <v>30.359762182196583</v>
       </c>
       <c r="CB20" s="3">
-        <f t="shared" si="19"/>
-        <v>40.372307011212015</v>
+        <f t="shared" si="18"/>
+        <v>30.056164560374619</v>
       </c>
       <c r="CC20" s="3">
-        <f t="shared" si="19"/>
-        <v>39.968583941099894</v>
+        <f t="shared" si="18"/>
+        <v>29.755602914770872</v>
       </c>
       <c r="CD20" s="3">
-        <f t="shared" si="19"/>
-        <v>39.568898101688895</v>
+        <f t="shared" si="18"/>
+        <v>29.458046885623162</v>
       </c>
       <c r="CE20" s="3">
-        <f t="shared" si="19"/>
-        <v>39.173209120672006</v>
+        <f t="shared" si="18"/>
+        <v>29.16346641676693</v>
       </c>
       <c r="CF20" s="3">
-        <f t="shared" si="19"/>
-        <v>38.781477029465286</v>
+        <f t="shared" si="18"/>
+        <v>28.87183175259926</v>
       </c>
       <c r="CG20" s="3">
-        <f t="shared" si="19"/>
-        <v>38.393662259170632</v>
+        <f t="shared" si="18"/>
+        <v>28.583113435073265</v>
       </c>
       <c r="CH20" s="3">
-        <f t="shared" si="19"/>
-        <v>38.009725636578928</v>
+        <f t="shared" si="18"/>
+        <v>28.297282300722532</v>
       </c>
       <c r="CI20" s="3">
-        <f t="shared" si="19"/>
-        <v>37.629628380213141</v>
+        <f t="shared" si="18"/>
+        <v>28.014309477715308</v>
       </c>
       <c r="CJ20" s="3">
-        <f t="shared" si="19"/>
-        <v>37.253332096411008</v>
+        <f t="shared" si="18"/>
+        <v>27.734166382938156</v>
       </c>
       <c r="CK20" s="3">
-        <f t="shared" si="19"/>
-        <v>36.880798775446898</v>
+        <f t="shared" si="18"/>
+        <v>27.456824719108774</v>
       </c>
       <c r="CL20" s="3">
-        <f t="shared" si="19"/>
-        <v>36.511990787692426</v>
+        <f t="shared" si="18"/>
+        <v>27.182256471917686</v>
       </c>
       <c r="CM20" s="3">
-        <f t="shared" si="19"/>
-        <v>36.146870879815502</v>
+        <f t="shared" si="18"/>
+        <v>26.910433907198509</v>
       </c>
       <c r="CN20" s="3">
-        <f t="shared" si="19"/>
-        <v>35.785402171017346</v>
+        <f t="shared" si="18"/>
+        <v>26.641329568126523</v>
       </c>
       <c r="CO20" s="3">
-        <f t="shared" si="19"/>
-        <v>35.427548149307171</v>
+        <f t="shared" si="18"/>
+        <v>26.374916272445258</v>
       </c>
       <c r="CP20" s="3">
-        <f t="shared" ref="CP20:EK20" si="20">CO20*(1+$AF$26)</f>
-        <v>35.073272667814102</v>
+        <f t="shared" ref="CP20:EK20" si="19">CO20*(1+$AF$25)</f>
+        <v>26.111167109720807</v>
       </c>
       <c r="CQ20" s="3">
-        <f t="shared" si="20"/>
-        <v>34.722539941135963</v>
+        <f t="shared" si="19"/>
+        <v>25.850055438623599</v>
       </c>
       <c r="CR20" s="3">
-        <f t="shared" si="20"/>
-        <v>34.375314541724606</v>
+        <f t="shared" si="19"/>
+        <v>25.591554884237361</v>
       </c>
       <c r="CS20" s="3">
-        <f t="shared" si="20"/>
-        <v>34.03156139630736</v>
+        <f t="shared" si="19"/>
+        <v>25.335639335394987</v>
       </c>
       <c r="CT20" s="3">
-        <f t="shared" si="20"/>
-        <v>33.691245782344289</v>
+        <f t="shared" si="19"/>
+        <v>25.082282942041036</v>
       </c>
       <c r="CU20" s="3">
-        <f t="shared" si="20"/>
-        <v>33.354333324520844</v>
+        <f t="shared" si="19"/>
+        <v>24.831460112620626</v>
       </c>
       <c r="CV20" s="3">
-        <f t="shared" si="20"/>
-        <v>33.020789991275635</v>
+        <f t="shared" si="19"/>
+        <v>24.583145511494418</v>
       </c>
       <c r="CW20" s="3">
-        <f t="shared" si="20"/>
-        <v>32.690582091362877</v>
+        <f t="shared" si="19"/>
+        <v>24.337314056379473</v>
       </c>
       <c r="CX20" s="3">
-        <f t="shared" si="20"/>
-        <v>32.363676270449247</v>
+        <f t="shared" si="19"/>
+        <v>24.093940915815679</v>
       </c>
       <c r="CY20" s="3">
-        <f t="shared" si="20"/>
-        <v>32.040039507744751</v>
+        <f t="shared" si="19"/>
+        <v>23.853001506657524</v>
       </c>
       <c r="CZ20" s="3">
-        <f t="shared" si="20"/>
-        <v>31.719639112667302</v>
+        <f t="shared" si="19"/>
+        <v>23.614471491590947</v>
       </c>
       <c r="DA20" s="3">
-        <f t="shared" si="20"/>
-        <v>31.402442721540631</v>
+        <f t="shared" si="19"/>
+        <v>23.378326776675038</v>
       </c>
       <c r="DB20" s="3">
-        <f t="shared" si="20"/>
-        <v>31.088418294325223</v>
+        <f t="shared" si="19"/>
+        <v>23.144543508908288</v>
       </c>
       <c r="DC20" s="3">
-        <f t="shared" si="20"/>
-        <v>30.777534111381971</v>
+        <f t="shared" si="19"/>
+        <v>22.913098073819206</v>
       </c>
       <c r="DD20" s="3">
-        <f t="shared" si="20"/>
-        <v>30.46975877026815</v>
+        <f t="shared" si="19"/>
+        <v>22.683967093081016</v>
       </c>
       <c r="DE20" s="3">
-        <f t="shared" si="20"/>
-        <v>30.16506118256547</v>
+        <f t="shared" si="19"/>
+        <v>22.457127422150204</v>
       </c>
       <c r="DF20" s="3">
-        <f t="shared" si="20"/>
-        <v>29.863410570739816</v>
+        <f t="shared" si="19"/>
+        <v>22.232556147928701</v>
       </c>
       <c r="DG20" s="3">
-        <f t="shared" si="20"/>
-        <v>29.564776465032416</v>
+        <f t="shared" si="19"/>
+        <v>22.010230586449413</v>
       </c>
       <c r="DH20" s="3">
-        <f t="shared" si="20"/>
-        <v>29.26912870038209</v>
+        <f t="shared" si="19"/>
+        <v>21.79012828058492</v>
       </c>
       <c r="DI20" s="3">
-        <f t="shared" si="20"/>
-        <v>28.976437413378271</v>
+        <f t="shared" si="19"/>
+        <v>21.572226997779069</v>
       </c>
       <c r="DJ20" s="3">
-        <f t="shared" si="20"/>
-        <v>28.686673039244489</v>
+        <f t="shared" si="19"/>
+        <v>21.356504727801276</v>
       </c>
       <c r="DK20" s="3">
-        <f t="shared" si="20"/>
-        <v>28.399806308852042</v>
+        <f t="shared" si="19"/>
+        <v>21.142939680523263</v>
       </c>
       <c r="DL20" s="3">
-        <f t="shared" si="20"/>
-        <v>28.115808245763521</v>
+        <f t="shared" si="19"/>
+        <v>20.93151028371803</v>
       </c>
       <c r="DM20" s="3">
-        <f t="shared" si="20"/>
-        <v>27.834650163305884</v>
+        <f t="shared" si="19"/>
+        <v>20.722195180880849</v>
       </c>
       <c r="DN20" s="3">
-        <f t="shared" si="20"/>
-        <v>27.556303661672825</v>
+        <f t="shared" si="19"/>
+        <v>20.514973229072041</v>
       </c>
       <c r="DO20" s="3">
-        <f t="shared" si="20"/>
-        <v>27.280740625056097</v>
+        <f t="shared" si="19"/>
+        <v>20.30982349678132</v>
       </c>
       <c r="DP20" s="3">
-        <f t="shared" si="20"/>
-        <v>27.007933218805537</v>
+        <f t="shared" si="19"/>
+        <v>20.106725261813505</v>
       </c>
       <c r="DQ20" s="3">
-        <f t="shared" si="20"/>
-        <v>26.737853886617483</v>
+        <f t="shared" si="19"/>
+        <v>19.905658009195371</v>
       </c>
       <c r="DR20" s="3">
-        <f t="shared" si="20"/>
-        <v>26.470475347751307</v>
+        <f t="shared" si="19"/>
+        <v>19.706601429103415</v>
       </c>
       <c r="DS20" s="3">
-        <f t="shared" si="20"/>
-        <v>26.205770594273794</v>
+        <f t="shared" si="19"/>
+        <v>19.50953541481238</v>
       </c>
       <c r="DT20" s="3">
-        <f t="shared" si="20"/>
-        <v>25.943712888331056</v>
+        <f t="shared" si="19"/>
+        <v>19.314440060664257</v>
       </c>
       <c r="DU20" s="3">
-        <f t="shared" si="20"/>
-        <v>25.684275759447747</v>
+        <f t="shared" si="19"/>
+        <v>19.121295660057616</v>
       </c>
       <c r="DV20" s="3">
-        <f t="shared" si="20"/>
-        <v>25.42743300185327</v>
+        <f t="shared" si="19"/>
+        <v>18.930082703457039</v>
       </c>
       <c r="DW20" s="3">
-        <f t="shared" si="20"/>
-        <v>25.173158671834738</v>
+        <f t="shared" si="19"/>
+        <v>18.740781876422467</v>
       </c>
       <c r="DX20" s="3">
-        <f t="shared" si="20"/>
-        <v>24.921427085116392</v>
+        <f t="shared" si="19"/>
+        <v>18.553374057658242</v>
       </c>
       <c r="DY20" s="3">
-        <f t="shared" si="20"/>
-        <v>24.672212814265226</v>
+        <f t="shared" si="19"/>
+        <v>18.367840317081662</v>
       </c>
       <c r="DZ20" s="3">
-        <f t="shared" si="20"/>
-        <v>24.425490686122572</v>
+        <f t="shared" si="19"/>
+        <v>18.184161913910845</v>
       </c>
       <c r="EA20" s="3">
-        <f t="shared" si="20"/>
-        <v>24.181235779261346</v>
+        <f t="shared" si="19"/>
+        <v>18.002320294771735</v>
       </c>
       <c r="EB20" s="3">
-        <f t="shared" si="20"/>
-        <v>23.939423421468732</v>
+        <f t="shared" si="19"/>
+        <v>17.822297091824019</v>
       </c>
       <c r="EC20" s="3">
-        <f t="shared" si="20"/>
-        <v>23.700029187254046</v>
+        <f t="shared" si="19"/>
+        <v>17.644074120905778</v>
       </c>
       <c r="ED20" s="3">
-        <f t="shared" si="20"/>
-        <v>23.463028895381505</v>
+        <f t="shared" si="19"/>
+        <v>17.467633379696721</v>
       </c>
       <c r="EE20" s="3">
-        <f t="shared" si="20"/>
-        <v>23.228398606427689</v>
+        <f t="shared" si="19"/>
+        <v>17.292957045899755</v>
       </c>
       <c r="EF20" s="3">
-        <f t="shared" si="20"/>
-        <v>22.996114620363411</v>
+        <f t="shared" si="19"/>
+        <v>17.120027475440757</v>
       </c>
       <c r="EG20" s="3">
-        <f t="shared" si="20"/>
-        <v>22.766153474159776</v>
+        <f t="shared" si="19"/>
+        <v>16.948827200686349</v>
       </c>
       <c r="EH20" s="3">
-        <f t="shared" si="20"/>
-        <v>22.538491939418179</v>
+        <f t="shared" si="19"/>
+        <v>16.779338928679486</v>
       </c>
       <c r="EI20" s="3">
-        <f t="shared" si="20"/>
-        <v>22.313107020023999</v>
+        <f t="shared" si="19"/>
+        <v>16.61154553939269</v>
       </c>
       <c r="EJ20" s="3">
-        <f t="shared" si="20"/>
-        <v>22.08997594982376</v>
+        <f t="shared" si="19"/>
+        <v>16.445430083998762</v>
       </c>
       <c r="EK20" s="3">
-        <f t="shared" si="20"/>
-        <v>21.869076190325522</v>
+        <f t="shared" si="19"/>
+        <v>16.280975783158773</v>
       </c>
     </row>
     <row r="21" spans="2:141" x14ac:dyDescent="0.3">
@@ -3045,10 +3040,12 @@
         <v>30.4</v>
       </c>
       <c r="M21" s="6">
-        <v>30.4</v>
+        <f>36.9</f>
+        <v>36.9</v>
       </c>
       <c r="N21" s="6">
-        <v>30.4</v>
+        <f>36.9</f>
+        <v>36.9</v>
       </c>
       <c r="P21" s="6">
         <v>3.2</v>
@@ -3057,37 +3054,48 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="R21" s="6">
-        <v>30.4</v>
+        <f t="shared" ref="R21:AB21" si="20">36.9</f>
+        <v>36.9</v>
       </c>
       <c r="S21" s="6">
-        <v>30.4</v>
+        <f t="shared" si="20"/>
+        <v>36.9</v>
       </c>
       <c r="T21" s="6">
-        <v>30.4</v>
+        <f t="shared" si="20"/>
+        <v>36.9</v>
       </c>
       <c r="U21" s="6">
-        <v>30.4</v>
+        <f t="shared" si="20"/>
+        <v>36.9</v>
       </c>
       <c r="V21" s="6">
-        <v>30.4</v>
+        <f t="shared" si="20"/>
+        <v>36.9</v>
       </c>
       <c r="W21" s="6">
-        <v>30.4</v>
+        <f t="shared" si="20"/>
+        <v>36.9</v>
       </c>
       <c r="X21" s="6">
-        <v>30.4</v>
+        <f t="shared" si="20"/>
+        <v>36.9</v>
       </c>
       <c r="Y21" s="6">
-        <v>30.4</v>
+        <f t="shared" si="20"/>
+        <v>36.9</v>
       </c>
       <c r="Z21" s="6">
-        <v>30.4</v>
+        <f t="shared" si="20"/>
+        <v>36.9</v>
       </c>
       <c r="AA21" s="6">
-        <v>30.4</v>
+        <f t="shared" si="20"/>
+        <v>36.9</v>
       </c>
       <c r="AB21" s="6">
-        <v>30.4</v>
+        <f t="shared" si="20"/>
+        <v>36.9</v>
       </c>
     </row>
     <row r="22" spans="2:141" x14ac:dyDescent="0.3">
@@ -3132,11 +3140,11 @@
       </c>
       <c r="M22" s="10">
         <f t="shared" si="21"/>
-        <v>-0.26513157894736844</v>
+        <v>4.3360433604336036E-2</v>
       </c>
       <c r="N22" s="10">
         <f t="shared" si="21"/>
-        <v>-0.30157894736842106</v>
+        <v>-0.18970189701897019</v>
       </c>
       <c r="P22" s="9">
         <f>P20/P21</f>
@@ -3148,588 +3156,553 @@
       </c>
       <c r="R22" s="9">
         <f>R20/R21</f>
-        <v>-0.90223684210526323</v>
+        <v>-0.4227642276422765</v>
       </c>
       <c r="S22" s="9">
         <f>S20/S21</f>
-        <v>-1.2003289473684209</v>
+        <v>-0.65886178861788625</v>
       </c>
       <c r="T22" s="9">
         <f t="shared" ref="T22:AB22" si="22">T20/T21</f>
-        <v>-1.4716513157894735</v>
+        <v>-0.82576205962059612</v>
       </c>
       <c r="U22" s="9">
         <f t="shared" si="22"/>
-        <v>-1.1920697368421052</v>
+        <v>-0.69863121951219531</v>
       </c>
       <c r="V22" s="9">
         <f t="shared" si="22"/>
-        <v>-0.85205776315789472</v>
+        <v>-0.52572508401084028</v>
       </c>
       <c r="W22" s="9">
         <f t="shared" si="22"/>
-        <v>-0.65341010526315824</v>
+        <v>-0.39747101138211433</v>
       </c>
       <c r="X22" s="9">
         <f t="shared" si="22"/>
-        <v>-0.29951568421052677</v>
+        <v>-0.16711311436314369</v>
       </c>
       <c r="Y22" s="9">
         <f t="shared" si="22"/>
-        <v>0.2104545263157889</v>
+        <v>0.16599125680216822</v>
       </c>
       <c r="Z22" s="9">
         <f t="shared" si="22"/>
-        <v>0.72762911578947298</v>
+        <v>0.50386679536043311</v>
       </c>
       <c r="AA22" s="9">
         <f t="shared" si="22"/>
-        <v>1.3870369755789473</v>
+        <v>0.93468697626016195</v>
       </c>
       <c r="AB22" s="9">
         <f t="shared" si="22"/>
-        <v>2.239648504399999</v>
+        <v>1.3736531128047684</v>
       </c>
     </row>
     <row r="24" spans="2:141" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11">
-        <f t="shared" ref="H24:I24" si="23">H3/G3-1</f>
-        <v>1.3333333333333335</v>
-      </c>
-      <c r="I24" s="11">
+        <v>38</v>
+      </c>
+      <c r="K24" s="11">
+        <f>K3/G3-1</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="L24" s="11">
+        <f t="shared" ref="L24:N24" si="23">L3/H3-1</f>
+        <v>0.50000000000000022</v>
+      </c>
+      <c r="M24" s="11">
         <f t="shared" si="23"/>
-        <v>7.1428571428571397E-2</v>
-      </c>
-      <c r="J24" s="11">
-        <f>J3/I3-1</f>
-        <v>0.39999999999999969</v>
-      </c>
-      <c r="K24" s="11">
-        <f t="shared" ref="K24:N24" si="24">K3/J3-1</f>
-        <v>-4.761904761904745E-2</v>
-      </c>
-      <c r="L24" s="11">
+        <v>0.40000000000000013</v>
+      </c>
+      <c r="N24" s="11">
+        <f t="shared" si="23"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11">
+        <f t="shared" ref="R24:AB24" si="24">R3/Q3-1</f>
+        <v>0.59464285714285725</v>
+      </c>
+      <c r="S24" s="11">
         <f t="shared" si="24"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="M24" s="11">
+        <v>1</v>
+      </c>
+      <c r="T24" s="11">
         <f t="shared" si="24"/>
-        <v>0.4285714285714286</v>
-      </c>
-      <c r="N24" s="11">
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="U24" s="11">
         <f t="shared" si="24"/>
-        <v>0.39999999999999969</v>
-      </c>
-      <c r="R24" s="11">
-        <f>R3/Q3-1</f>
-        <v>1.0178571428571428</v>
-      </c>
-      <c r="S24" s="11">
-        <f t="shared" ref="S24:AB24" si="25">S3/R3-1</f>
-        <v>1</v>
-      </c>
-      <c r="T24" s="11">
-        <f t="shared" si="25"/>
-        <v>0.89999999999999969</v>
-      </c>
-      <c r="U24" s="11">
-        <f t="shared" si="25"/>
         <v>0.8</v>
       </c>
       <c r="V24" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.7</v>
       </c>
       <c r="W24" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="X24" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.5</v>
       </c>
       <c r="Y24" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.39999999999999991</v>
       </c>
       <c r="Z24" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="AA24" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AB24" s="11">
-        <f t="shared" si="25"/>
-        <v>0.19999999999999996</v>
+        <f t="shared" si="24"/>
+        <v>0.14999999999999991</v>
       </c>
     </row>
     <row r="25" spans="2:141" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="G25" s="11">
+        <f t="shared" ref="G25:H25" si="25">G5/G3</f>
+        <v>0.33333333333333326</v>
+      </c>
+      <c r="H25" s="11">
+        <f t="shared" si="25"/>
+        <v>0.28571428571428564</v>
+      </c>
+      <c r="I25" s="11">
+        <f>I5/I3</f>
+        <v>0.26666666666666661</v>
+      </c>
+      <c r="J25" s="11">
+        <f>J5/J3</f>
+        <v>0.25</v>
       </c>
       <c r="K25" s="11">
-        <f>K3/G3-1</f>
-        <v>2.3333333333333335</v>
+        <f t="shared" ref="K25:N25" si="26">K5/K3</f>
+        <v>0.25</v>
       </c>
       <c r="L25" s="11">
-        <f t="shared" ref="L25:N25" si="26">L3/H3-1</f>
-        <v>0.50000000000000022</v>
+        <f t="shared" si="26"/>
+        <v>0.38095238095238093</v>
       </c>
       <c r="M25" s="11">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>0.38095238095238093</v>
       </c>
       <c r="N25" s="11">
         <f t="shared" si="26"/>
-        <v>1</v>
-      </c>
-      <c r="R25" s="11"/>
-      <c r="S25" s="11"/>
-      <c r="T25" s="11"/>
-      <c r="U25" s="11"/>
-      <c r="V25" s="11"/>
-      <c r="W25" s="11"/>
-      <c r="X25" s="11"/>
-      <c r="Y25" s="11"/>
-      <c r="Z25" s="11"/>
-      <c r="AA25" s="11"/>
-      <c r="AB25" s="11"/>
+        <v>0.3</v>
+      </c>
+      <c r="Q25" s="11">
+        <f t="shared" ref="Q25:R25" si="27">Q5/Q3</f>
+        <v>0.28571428571428564</v>
+      </c>
+      <c r="R25" s="11">
+        <f t="shared" si="27"/>
+        <v>0.32687569988801796</v>
+      </c>
+      <c r="S25" s="11">
+        <f t="shared" ref="S25:AB25" si="28">S5/S3</f>
+        <v>0.3</v>
+      </c>
+      <c r="T25" s="11">
+        <f t="shared" si="28"/>
+        <v>0.3</v>
+      </c>
+      <c r="U25" s="11">
+        <f t="shared" si="28"/>
+        <v>0.3</v>
+      </c>
+      <c r="V25" s="11">
+        <f t="shared" si="28"/>
+        <v>0.3</v>
+      </c>
+      <c r="W25" s="11">
+        <f t="shared" si="28"/>
+        <v>0.3</v>
+      </c>
+      <c r="X25" s="11">
+        <f t="shared" si="28"/>
+        <v>0.3</v>
+      </c>
+      <c r="Y25" s="11">
+        <f t="shared" si="28"/>
+        <v>0.3</v>
+      </c>
+      <c r="Z25" s="11">
+        <f t="shared" si="28"/>
+        <v>0.3</v>
+      </c>
+      <c r="AA25" s="11">
+        <f t="shared" si="28"/>
+        <v>0.3</v>
+      </c>
+      <c r="AB25" s="11">
+        <f t="shared" si="28"/>
+        <v>0.3</v>
+      </c>
+      <c r="AE25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF25" s="11">
+        <v>-0.01</v>
+      </c>
     </row>
     <row r="26" spans="2:141" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G26" s="11">
-        <f t="shared" ref="G26:H26" si="27">G5/G3</f>
-        <v>0.33333333333333326</v>
-      </c>
-      <c r="H26" s="11">
-        <f t="shared" si="27"/>
-        <v>0.28571428571428564</v>
-      </c>
-      <c r="I26" s="11">
-        <f>I5/I3</f>
-        <v>0.26666666666666661</v>
-      </c>
-      <c r="J26" s="11">
-        <f>J5/J3</f>
-        <v>0.25</v>
-      </c>
-      <c r="K26" s="11">
-        <f t="shared" ref="K26:N26" si="28">K5/K3</f>
-        <v>0.25</v>
-      </c>
-      <c r="L26" s="11">
-        <f t="shared" si="28"/>
-        <v>0.38095238095238093</v>
-      </c>
-      <c r="M26" s="11">
-        <f t="shared" si="28"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="N26" s="11">
-        <f t="shared" si="28"/>
-        <v>0.26</v>
-      </c>
-      <c r="Q26" s="11">
-        <f t="shared" ref="Q26:R26" si="29">Q5/Q3</f>
-        <v>0.28571428571428564</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="Q26" s="11"/>
       <c r="R26" s="11">
-        <f t="shared" si="29"/>
-        <v>0.28601769911504421</v>
+        <f t="shared" ref="R26" si="29">R7/Q7-1</f>
+        <v>0</v>
       </c>
       <c r="S26" s="11">
-        <f t="shared" ref="S26:AB26" si="30">S5/S3</f>
-        <v>0.3</v>
+        <f t="shared" ref="S26" si="30">S7/R7-1</f>
+        <v>19</v>
       </c>
       <c r="T26" s="11">
-        <f t="shared" si="30"/>
-        <v>0.3</v>
+        <f t="shared" ref="T26" si="31">T7/S7-1</f>
+        <v>1.5</v>
       </c>
       <c r="U26" s="11">
-        <f t="shared" si="30"/>
-        <v>0.3</v>
+        <f t="shared" ref="U26" si="32">U7/T7-1</f>
+        <v>0.8</v>
       </c>
       <c r="V26" s="11">
-        <f t="shared" si="30"/>
-        <v>0.3</v>
+        <f t="shared" ref="V26" si="33">V7/U7-1</f>
+        <v>0.44444444444444442</v>
       </c>
       <c r="W26" s="11">
-        <f t="shared" si="30"/>
-        <v>0.3</v>
+        <f t="shared" ref="W26" si="34">W7/V7-1</f>
+        <v>0.15384615384615374</v>
       </c>
       <c r="X26" s="11">
-        <f t="shared" si="30"/>
-        <v>0.3</v>
+        <f t="shared" ref="X26" si="35">X7/W7-1</f>
+        <v>0.1333333333333333</v>
       </c>
       <c r="Y26" s="11">
-        <f t="shared" si="30"/>
-        <v>0.3</v>
+        <f t="shared" ref="Y26" si="36">Y7/X7-1</f>
+        <v>0.11764705882352944</v>
       </c>
       <c r="Z26" s="11">
-        <f t="shared" si="30"/>
-        <v>0.3</v>
+        <f t="shared" ref="Z26" si="37">Z7/Y7-1</f>
+        <v>5.2631578947368363E-2</v>
       </c>
       <c r="AA26" s="11">
-        <f t="shared" si="30"/>
-        <v>0.3</v>
+        <f t="shared" ref="AA26" si="38">AA7/Z7-1</f>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AB26" s="11">
-        <f t="shared" si="30"/>
-        <v>0.3</v>
+        <f t="shared" ref="R26:AB28" si="39">AB7/AA7-1</f>
+        <v>4.7619047619047672E-2</v>
       </c>
       <c r="AE26" s="1" t="s">
         <v>48</v>
       </c>
       <c r="AF26" s="11">
-        <v>-0.01</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="27" spans="2:141" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-      <c r="Q27" s="11"/>
+        <v>42</v>
+      </c>
+      <c r="G27" s="11">
+        <f>G8/G3</f>
+        <v>0.33333333333333337</v>
+      </c>
+      <c r="H27" s="11">
+        <f t="shared" ref="H27:J27" si="40">H8/H3</f>
+        <v>0.28571428571428575</v>
+      </c>
+      <c r="I27" s="11">
+        <f t="shared" si="40"/>
+        <v>0.19999999999999998</v>
+      </c>
+      <c r="J27" s="11">
+        <f t="shared" si="40"/>
+        <v>9.5238095238095261E-2</v>
+      </c>
+      <c r="K27" s="11">
+        <f t="shared" ref="K27:N27" si="41">K8/K3</f>
+        <v>0.1</v>
+      </c>
+      <c r="L27" s="11">
+        <f t="shared" si="41"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="M27" s="11">
+        <f t="shared" si="41"/>
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="N27" s="11">
+        <f t="shared" si="41"/>
+        <v>0.3</v>
+      </c>
+      <c r="Q27" s="11">
+        <f t="shared" ref="Q27:R27" si="42">Q8/Q3</f>
+        <v>0.19642857142857145</v>
+      </c>
       <c r="R27" s="11">
-        <f t="shared" ref="R27" si="31">R7/Q7-1</f>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>0.19249720044792831</v>
       </c>
       <c r="S27" s="11">
-        <f t="shared" ref="S27" si="32">S7/R7-1</f>
-        <v>19</v>
+        <f t="shared" ref="S27:AB27" si="43">S8/S3</f>
+        <v>0.25</v>
       </c>
       <c r="T27" s="11">
-        <f t="shared" ref="T27" si="33">T7/S7-1</f>
-        <v>1.5</v>
+        <f t="shared" si="43"/>
+        <v>0.23</v>
       </c>
       <c r="U27" s="11">
-        <f t="shared" ref="U27" si="34">U7/T7-1</f>
-        <v>0.8</v>
+        <f t="shared" si="43"/>
+        <v>0.21</v>
       </c>
       <c r="V27" s="11">
-        <f t="shared" ref="V27" si="35">V7/U7-1</f>
-        <v>0.44444444444444442</v>
+        <f t="shared" si="43"/>
+        <v>0.19</v>
       </c>
       <c r="W27" s="11">
-        <f t="shared" ref="W27" si="36">W7/V7-1</f>
-        <v>0.15384615384615374</v>
+        <f t="shared" si="43"/>
+        <v>0.18</v>
       </c>
       <c r="X27" s="11">
-        <f t="shared" ref="X27" si="37">X7/W7-1</f>
-        <v>0.1333333333333333</v>
+        <f t="shared" si="43"/>
+        <v>0.17</v>
       </c>
       <c r="Y27" s="11">
-        <f t="shared" ref="Y27" si="38">Y7/X7-1</f>
-        <v>0.11764705882352944</v>
+        <f t="shared" si="43"/>
+        <v>0.16</v>
       </c>
       <c r="Z27" s="11">
-        <f t="shared" ref="Z27" si="39">Z7/Y7-1</f>
-        <v>5.2631578947368363E-2</v>
+        <f t="shared" si="43"/>
+        <v>0.16</v>
       </c>
       <c r="AA27" s="11">
-        <f t="shared" ref="AA27" si="40">AA7/Z7-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="43"/>
+        <v>0.15</v>
       </c>
       <c r="AB27" s="11">
-        <f t="shared" ref="R27:AB29" si="41">AB7/AA7-1</f>
-        <v>4.7619047619047672E-2</v>
+        <f t="shared" si="43"/>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AE27" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AF27" s="11">
-        <v>0.12</v>
+      <c r="AF27" s="6">
+        <f>NPV(AF26,R20:EK20)</f>
+        <v>53.213290765826692</v>
       </c>
     </row>
     <row r="28" spans="2:141" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G28" s="11">
-        <f>G8/G3</f>
-        <v>0.33333333333333337</v>
+        <f t="shared" ref="G28:H28" si="44">G9/C9-1</f>
+        <v>0.66666666666666674</v>
       </c>
       <c r="H28" s="11">
-        <f t="shared" ref="H28:J28" si="42">H8/H3</f>
-        <v>0.28571428571428575</v>
+        <f t="shared" si="44"/>
+        <v>2.25</v>
       </c>
       <c r="I28" s="11">
-        <f t="shared" si="42"/>
-        <v>0.19999999999999998</v>
-      </c>
-      <c r="J28" s="11">
-        <f t="shared" si="42"/>
-        <v>9.5238095238095261E-2</v>
+        <f>I9/E9-1</f>
+        <v>2.4999999999999996</v>
+      </c>
+      <c r="J28" s="11" t="e">
+        <f>J9/F9-1</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="K28" s="11">
-        <f t="shared" ref="K28:N28" si="43">K8/K3</f>
-        <v>0.1</v>
+        <f t="shared" ref="K28:N28" si="45">K9/G9-1</f>
+        <v>2.2000000000000002</v>
       </c>
       <c r="L28" s="11">
-        <f t="shared" si="43"/>
-        <v>0.14285714285714285</v>
+        <f t="shared" si="45"/>
+        <v>4.5384615384615383</v>
       </c>
       <c r="M28" s="11">
-        <f t="shared" si="43"/>
-        <v>0.3</v>
+        <f t="shared" si="45"/>
+        <v>2.3571428571428577</v>
       </c>
       <c r="N28" s="11">
-        <f t="shared" si="43"/>
-        <v>0.3</v>
+        <f t="shared" si="45"/>
+        <v>1.6923076923076916</v>
       </c>
       <c r="Q28" s="11">
-        <f t="shared" ref="Q28:R28" si="44">Q8/Q3</f>
-        <v>0.19642857142857145</v>
+        <f>Q9/P9-1</f>
+        <v>3.5</v>
       </c>
       <c r="R28" s="11">
-        <f t="shared" si="44"/>
-        <v>0.23539823008849556</v>
+        <f t="shared" si="39"/>
+        <v>2.5079365079365084</v>
       </c>
       <c r="S28" s="11">
-        <f t="shared" ref="S28:AB28" si="45">S8/S3</f>
-        <v>0.25</v>
+        <f t="shared" si="39"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="T28" s="11">
-        <f t="shared" si="45"/>
-        <v>0.23000000000000004</v>
+        <f t="shared" si="39"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="U28" s="11">
-        <f t="shared" si="45"/>
-        <v>0.21</v>
+        <f t="shared" si="39"/>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="V28" s="11">
-        <f t="shared" si="45"/>
-        <v>0.19</v>
+        <f t="shared" si="39"/>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="W28" s="11">
-        <f t="shared" si="45"/>
-        <v>0.18</v>
+        <f t="shared" si="39"/>
+        <v>0.10000000000000009</v>
       </c>
       <c r="X28" s="11">
-        <f t="shared" si="45"/>
-        <v>0.17</v>
+        <f t="shared" si="39"/>
+        <v>0.10000000000000009</v>
       </c>
       <c r="Y28" s="11">
-        <f t="shared" si="45"/>
-        <v>0.16</v>
+        <f t="shared" si="39"/>
+        <v>0.10000000000000009</v>
       </c>
       <c r="Z28" s="11">
-        <f t="shared" si="45"/>
-        <v>0.16</v>
+        <f t="shared" si="39"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AA28" s="11">
-        <f t="shared" si="45"/>
-        <v>0.15</v>
+        <f t="shared" si="39"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AB28" s="11">
-        <f t="shared" si="45"/>
-        <v>0.14000000000000001</v>
+        <f t="shared" si="39"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AE28" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AF28" s="6">
-        <f>NPV(AF27,R20:EK20)</f>
-        <v>55.431606635265183</v>
+        <f>Main!D8</f>
+        <v>81.099999999999994</v>
       </c>
     </row>
     <row r="29" spans="2:141" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="G29" s="11">
-        <f t="shared" ref="G29:H29" si="46">G9/C9-1</f>
-        <v>0.66666666666666674</v>
+        <f>G12/G3</f>
+        <v>-1.8333333333333335</v>
       </c>
       <c r="H29" s="11">
+        <f t="shared" ref="H29:N29" si="46">H12/H3</f>
+        <v>-1.0714285714285716</v>
+      </c>
+      <c r="I29" s="11">
         <f t="shared" si="46"/>
-        <v>2.25</v>
-      </c>
-      <c r="I29" s="11">
-        <f>I9/E9-1</f>
-        <v>2.4999999999999996</v>
-      </c>
-      <c r="J29" s="11" t="e">
-        <f>J9/F9-1</f>
-        <v>#DIV/0!</v>
+        <v>-1</v>
+      </c>
+      <c r="J29" s="11">
+        <f t="shared" si="46"/>
+        <v>-6.2261904761904772</v>
       </c>
       <c r="K29" s="11">
-        <f t="shared" ref="K29:N29" si="47">K9/G9-1</f>
-        <v>2.2000000000000002</v>
+        <f t="shared" si="46"/>
+        <v>-1.6</v>
       </c>
       <c r="L29" s="11">
+        <f t="shared" si="46"/>
+        <v>-3.4285714285714284</v>
+      </c>
+      <c r="M29" s="11">
+        <f t="shared" si="46"/>
+        <v>-2.3333333333333335</v>
+      </c>
+      <c r="N29" s="11">
+        <f t="shared" si="46"/>
+        <v>-2.5641025641025643</v>
+      </c>
+      <c r="Q29" s="11">
+        <f t="shared" ref="Q29:AB29" si="47">Q12/Q3</f>
+        <v>-3.0535714285714288</v>
+      </c>
+      <c r="R29" s="11">
         <f t="shared" si="47"/>
-        <v>4.5384615384615383</v>
-      </c>
-      <c r="M29" s="11">
+        <v>-2.4972004479283316</v>
+      </c>
+      <c r="S29" s="11">
         <f t="shared" si="47"/>
-        <v>4.7142857142857144</v>
-      </c>
-      <c r="N29" s="11">
+        <v>-1.3612541993281075</v>
+      </c>
+      <c r="T29" s="11">
         <f t="shared" si="47"/>
-        <v>2.4615384615384608</v>
-      </c>
-      <c r="Q29" s="11">
-        <f>Q9/P9-1</f>
-        <v>3.5</v>
-      </c>
-      <c r="R29" s="11">
-        <f t="shared" si="41"/>
-        <v>3.3492063492063489</v>
-      </c>
-      <c r="S29" s="11">
-        <f t="shared" si="41"/>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="T29" s="11">
-        <f t="shared" si="41"/>
-        <v>0.19999999999999996</v>
+        <v>-0.89793776153710136</v>
       </c>
       <c r="U29" s="11">
-        <f t="shared" si="41"/>
-        <v>-0.20000000000000007</v>
+        <f t="shared" si="47"/>
+        <v>-0.42205280839276255</v>
       </c>
       <c r="V29" s="11">
-        <f t="shared" si="41"/>
-        <v>-0.19999999999999996</v>
+        <f t="shared" si="47"/>
+        <v>-0.186822243563149</v>
       </c>
       <c r="W29" s="11">
-        <f t="shared" si="41"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="47"/>
+        <v>-8.8278584611188843E-2</v>
       </c>
       <c r="X29" s="11">
-        <f t="shared" si="41"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="47"/>
+        <v>-2.4743958315597385E-2</v>
       </c>
       <c r="Y29" s="11">
-        <f t="shared" si="41"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="47"/>
+        <v>1.7555605780291091E-2</v>
       </c>
       <c r="Z29" s="11">
-        <f t="shared" si="41"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="47"/>
+        <v>4.0992366778546827E-2</v>
       </c>
       <c r="AA29" s="11">
-        <f t="shared" si="41"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="47"/>
+        <v>6.3368320931228461E-2</v>
       </c>
       <c r="AB29" s="11">
-        <f t="shared" si="41"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="47"/>
+        <v>8.0981392944563468E-2</v>
       </c>
       <c r="AE29" s="1" t="s">
         <v>51</v>
       </c>
       <c r="AF29" s="6">
-        <f>Main!D8</f>
-        <v>5</v>
+        <f>AF27+AF28</f>
+        <v>134.31329076582668</v>
       </c>
     </row>
     <row r="30" spans="2:141" x14ac:dyDescent="0.3">
-      <c r="B30" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G30" s="11">
-        <f>G12/G3</f>
-        <v>-1.8333333333333335</v>
-      </c>
-      <c r="H30" s="11">
-        <f t="shared" ref="H30:N30" si="48">H12/H3</f>
-        <v>-1.0714285714285716</v>
-      </c>
-      <c r="I30" s="11">
-        <f t="shared" si="48"/>
-        <v>-1</v>
-      </c>
-      <c r="J30" s="11">
-        <f t="shared" si="48"/>
-        <v>-6.2261904761904772</v>
-      </c>
-      <c r="K30" s="11">
-        <f t="shared" si="48"/>
-        <v>-1.6</v>
-      </c>
-      <c r="L30" s="11">
-        <f t="shared" si="48"/>
-        <v>-3.4285714285714284</v>
-      </c>
-      <c r="M30" s="11">
-        <f t="shared" si="48"/>
-        <v>-2.686666666666667</v>
-      </c>
-      <c r="N30" s="11">
-        <f t="shared" si="48"/>
-        <v>-2.1828571428571428</v>
-      </c>
-      <c r="Q30" s="11">
-        <f t="shared" ref="Q30:AB30" si="49">Q12/Q3</f>
-        <v>-3.0535714285714288</v>
-      </c>
-      <c r="R30" s="11">
-        <f t="shared" si="49"/>
-        <v>-2.4449557522123895</v>
-      </c>
-      <c r="S30" s="11">
-        <f t="shared" si="49"/>
-        <v>-1.6146017699115043</v>
-      </c>
-      <c r="T30" s="11">
-        <f t="shared" si="49"/>
-        <v>-1.041877037727061</v>
-      </c>
-      <c r="U30" s="11">
-        <f t="shared" si="49"/>
-        <v>-0.46885732029188015</v>
-      </c>
-      <c r="V30" s="11">
-        <f t="shared" si="49"/>
-        <v>-0.19713291992779103</v>
-      </c>
-      <c r="W30" s="11">
-        <f t="shared" si="49"/>
-        <v>-9.448350183110045E-2</v>
-      </c>
-      <c r="X30" s="11">
-        <f t="shared" si="49"/>
-        <v>-2.8873434381256561E-2</v>
-      </c>
-      <c r="Y30" s="11">
-        <f t="shared" si="49"/>
-        <v>1.4491358826820034E-2</v>
-      </c>
-      <c r="Z30" s="11">
-        <f t="shared" si="49"/>
-        <v>3.8540518775593668E-2</v>
-      </c>
-      <c r="AA30" s="11">
-        <f t="shared" si="49"/>
-        <v>6.1222953928644498E-2</v>
-      </c>
-      <c r="AB30" s="11">
-        <f t="shared" si="49"/>
-        <v>8.2380582743060302E-2</v>
-      </c>
       <c r="AE30" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AF30" s="6">
-        <f>AF28+AF29</f>
-        <v>60.431606635265183</v>
+      <c r="AF30" s="4">
+        <f>AF29/AB21</f>
+        <v>3.6399265790196935</v>
       </c>
     </row>
     <row r="31" spans="2:141" x14ac:dyDescent="0.3">
@@ -3737,59 +3710,58 @@
         <v>53</v>
       </c>
       <c r="AF31" s="4">
-        <f>AF30/AB21</f>
-        <v>1.9878817972126706</v>
-      </c>
-    </row>
-    <row r="32" spans="2:141" x14ac:dyDescent="0.3">
-      <c r="AE32" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF32" s="4">
         <f>Main!D3</f>
-        <v>14.97</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="L33" s="12">
+        <v>7.88</v>
+      </c>
+    </row>
+    <row r="32" spans="2:141" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="L32" s="12">
         <f>52.4</f>
         <v>52.4</v>
       </c>
-      <c r="AE33" s="12" t="s">
+      <c r="M32" s="12">
+        <v>113.1</v>
+      </c>
+      <c r="R32" s="12">
+        <v>113.1</v>
+      </c>
+      <c r="AE32" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF32" s="14">
+        <f>AF30/AF31-1</f>
+        <v>-0.53808038337313535</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="AE33" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AF33" s="13">
-        <f>AF31/AF32-1</f>
-        <v>-0.86720896478205278</v>
+      <c r="AF33" s="7" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="AE34" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AF34" s="7" t="s">
-        <v>58</v>
+      <c r="B34" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L34" s="13"/>
+      <c r="R34" s="13">
+        <f>Main!$D$9/Model!R32</f>
+        <v>1.8538638373121132</v>
       </c>
     </row>
     <row r="35" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="14">
-        <f>Main!D9/Model!L33</f>
-        <v>8.5894656488549632</v>
-      </c>
-    </row>
-    <row r="36" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L36" s="11">
-        <f>L33/Main!D9-1</f>
-        <v>-0.88357832246138535</v>
+      <c r="L35" s="11"/>
+      <c r="R35" s="11">
+        <f>R32/Main!$D$9-1</f>
+        <v>-0.46058605822427412</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/UMAC.xlsx
+++ b/Financial Analysis/UMAC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C6ABCB-B9BE-4A5E-BCF1-550E046D9D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F51D983-820B-4A8B-9F5D-F3EB2622B83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{1911E082-F3EB-4149-9E06-B163ACF315BA}"/>
   </bookViews>
@@ -775,14 +775,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>7.88</v>
+        <v>13.02</v>
       </c>
       <c r="E3" s="5">
-        <v>45983</v>
+        <v>46071</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45983</v>
+        <v>46071</v>
       </c>
       <c r="G3" s="5">
         <v>46107</v>
@@ -806,7 +806,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>290.77199999999999</v>
+        <v>480.43799999999999</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -847,7 +847,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>209.672</v>
+        <v>399.33799999999997</v>
       </c>
     </row>
   </sheetData>
@@ -3417,7 +3417,7 @@
         <v>48</v>
       </c>
       <c r="AF26" s="11">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="27" spans="2:141" x14ac:dyDescent="0.3">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="AF27" s="6">
         <f>NPV(AF26,R20:EK20)</f>
-        <v>53.213290765826692</v>
+        <v>75.462936035448152</v>
       </c>
     </row>
     <row r="28" spans="2:141" x14ac:dyDescent="0.3">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AF29" s="6">
         <f>AF27+AF28</f>
-        <v>134.31329076582668</v>
+        <v>156.56293603544816</v>
       </c>
     </row>
     <row r="30" spans="2:141" x14ac:dyDescent="0.3">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AF30" s="4">
         <f>AF29/AB21</f>
-        <v>3.6399265790196935</v>
+        <v>4.2428979955406003</v>
       </c>
     </row>
     <row r="31" spans="2:141" x14ac:dyDescent="0.3">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AF31" s="4">
         <f>Main!D3</f>
-        <v>7.88</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="32" spans="2:141" s="12" customFormat="1" x14ac:dyDescent="0.3">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AF32" s="14">
         <f>AF30/AF31-1</f>
-        <v>-0.53808038337313535</v>
+        <v>-0.67412457791546854</v>
       </c>
     </row>
     <row r="33" spans="2:32" x14ac:dyDescent="0.3">
@@ -3751,7 +3751,7 @@
       <c r="L34" s="13"/>
       <c r="R34" s="13">
         <f>Main!$D$9/Model!R32</f>
-        <v>1.8538638373121132</v>
+        <v>3.5308399646330679</v>
       </c>
     </row>
     <row r="35" spans="2:32" x14ac:dyDescent="0.3">
@@ -3761,7 +3761,7 @@
       <c r="L35" s="11"/>
       <c r="R35" s="11">
         <f>R32/Main!$D$9-1</f>
-        <v>-0.46058605822427412</v>
+        <v>-0.71678127300682637</v>
       </c>
     </row>
   </sheetData>
